--- a/data/CS7/Market Data/CS7_market_data.xlsx
+++ b/data/CS7/Market Data/CS7_market_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3229D8C7-7971-4251-84C9-F4601D750D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3764F0C-D9D2-4183-9609-11D460B33DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="13656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21375" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Growth Factors" sheetId="1" r:id="rId1"/>
@@ -1565,76 +1565,76 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>45.875</v>
+        <v>57.62807500000001</v>
       </c>
       <c r="D2" s="1">
-        <v>43.09</v>
+        <v>55.55</v>
       </c>
       <c r="E2" s="1">
-        <v>41.05</v>
+        <v>53.603549999999998</v>
       </c>
       <c r="F2" s="1">
-        <v>40</v>
+        <v>56.433562500000001</v>
       </c>
       <c r="G2" s="1">
-        <v>39.799999999999997</v>
+        <v>53.282600000000002</v>
       </c>
       <c r="H2" s="1">
-        <v>40.549999999999997</v>
+        <v>54.786250000000003</v>
       </c>
       <c r="I2" s="1">
-        <v>42.954999999999998</v>
+        <v>60.200399999999988</v>
       </c>
       <c r="J2" s="1">
-        <v>51.024999999999999</v>
+        <v>61.536774999999999</v>
       </c>
       <c r="K2" s="1">
-        <v>56.92</v>
+        <v>56.202299999999994</v>
       </c>
       <c r="L2" s="1">
-        <v>55</v>
+        <v>51.013837500000001</v>
       </c>
       <c r="M2" s="1">
-        <v>48.814999999999998</v>
+        <v>43.947337500000003</v>
       </c>
       <c r="N2" s="1">
-        <v>43.09</v>
+        <v>42.340462500000001</v>
       </c>
       <c r="O2" s="1">
-        <v>41.945</v>
+        <v>36.816000000000003</v>
       </c>
       <c r="P2" s="1">
-        <v>41.09</v>
+        <v>36.565650000000012</v>
       </c>
       <c r="Q2" s="1">
-        <v>41.5</v>
+        <v>34.282850000000003</v>
       </c>
       <c r="R2" s="1">
-        <v>42.5</v>
+        <v>34.995800000000003</v>
       </c>
       <c r="S2" s="1">
-        <v>48.814999999999998</v>
+        <v>41.176437499999999</v>
       </c>
       <c r="T2" s="1">
-        <v>59.25</v>
+        <v>48.501249999999999</v>
       </c>
       <c r="U2" s="1">
-        <v>64.465000000000003</v>
+        <v>59.501250000000006</v>
       </c>
       <c r="V2" s="1">
-        <v>66.155000000000001</v>
+        <v>65.750237499999997</v>
       </c>
       <c r="W2" s="1">
-        <v>58.965000000000003</v>
+        <v>72.171750000000003</v>
       </c>
       <c r="X2" s="1">
-        <v>54.164999999999999</v>
+        <v>60.631374999999998</v>
       </c>
       <c r="Y2" s="1">
-        <v>50</v>
+        <v>62.711999999999996</v>
       </c>
       <c r="Z2" s="1">
-        <v>46.63</v>
+        <v>61.610174999999998</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -1645,76 +1645,76 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>44.49</v>
+        <v>55.345775000000003</v>
       </c>
       <c r="D3" s="1">
-        <v>43.225000000000001</v>
+        <v>58.327500000000001</v>
       </c>
       <c r="E3" s="1">
-        <v>42.494999999999997</v>
+        <v>57.432374999999993</v>
       </c>
       <c r="F3" s="1">
-        <v>41.5</v>
+        <v>53.2087875</v>
       </c>
       <c r="G3" s="1">
-        <v>41.57</v>
+        <v>53.826300000000003</v>
       </c>
       <c r="H3" s="1">
-        <v>42.5</v>
+        <v>57.525562499999999</v>
       </c>
       <c r="I3" s="1">
-        <v>44.5</v>
+        <v>60.200399999999988</v>
       </c>
       <c r="J3" s="1">
-        <v>50</v>
+        <v>62.755324999999992</v>
       </c>
       <c r="K3" s="1">
-        <v>52.384999999999998</v>
+        <v>59.040799999999997</v>
       </c>
       <c r="L3" s="1">
-        <v>52.5</v>
+        <v>49.498575000000002</v>
       </c>
       <c r="M3" s="1">
-        <v>50</v>
+        <v>45.279075000000006</v>
       </c>
       <c r="N3" s="1">
-        <v>47.29</v>
+        <v>41.5020375</v>
       </c>
       <c r="O3" s="1">
-        <v>46</v>
+        <v>37.1995</v>
       </c>
       <c r="P3" s="1">
-        <v>45.89</v>
+        <v>36.196300000000008</v>
       </c>
       <c r="Q3" s="1">
-        <v>45.05</v>
+        <v>33.583200000000005</v>
       </c>
       <c r="R3" s="1">
-        <v>46.005000000000003</v>
+        <v>36.781300000000002</v>
       </c>
       <c r="S3" s="1">
-        <v>50.49</v>
+        <v>39.953375000000008</v>
       </c>
       <c r="T3" s="1">
-        <v>53.55</v>
+        <v>46.076187499999996</v>
       </c>
       <c r="U3" s="1">
-        <v>63</v>
+        <v>57.716212500000005</v>
       </c>
       <c r="V3" s="1">
-        <v>59.734999999999999</v>
+        <v>69.817262499999998</v>
       </c>
       <c r="W3" s="1">
-        <v>55</v>
+        <v>68.047650000000004</v>
       </c>
       <c r="X3" s="1">
-        <v>51.13</v>
+        <v>62.546049999999994</v>
       </c>
       <c r="Y3" s="1">
-        <v>49</v>
+        <v>59.696999999999996</v>
       </c>
       <c r="Z3" s="1">
-        <v>47.744999999999997</v>
+        <v>60.365524999999998</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
@@ -1725,76 +1725,76 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>46.164999999999999</v>
+        <v>58.769225000000006</v>
       </c>
       <c r="D4" s="1">
-        <v>45.06</v>
+        <v>53.327999999999996</v>
       </c>
       <c r="E4" s="1">
-        <v>43.505000000000003</v>
+        <v>56.338424999999987</v>
       </c>
       <c r="F4" s="1">
-        <v>42.9</v>
+        <v>54.283712499999993</v>
       </c>
       <c r="G4" s="1">
-        <v>42.5</v>
+        <v>57.088500000000003</v>
       </c>
       <c r="H4" s="1">
-        <v>43.15</v>
+        <v>55.334112499999989</v>
       </c>
       <c r="I4" s="1">
-        <v>47.5</v>
+        <v>56.727299999999993</v>
       </c>
       <c r="J4" s="1">
-        <v>51.97</v>
+        <v>60.318224999999991</v>
       </c>
       <c r="K4" s="1">
-        <v>60.7</v>
+        <v>56.77</v>
       </c>
       <c r="L4" s="1">
-        <v>60.7</v>
+        <v>53.034187500000002</v>
       </c>
       <c r="M4" s="1">
-        <v>52.69</v>
+        <v>45.279075000000006</v>
       </c>
       <c r="N4" s="1">
-        <v>51.484999999999999</v>
+        <v>39.825187499999998</v>
       </c>
       <c r="O4" s="1">
-        <v>49.994999999999997</v>
+        <v>37.1995</v>
       </c>
       <c r="P4" s="1">
-        <v>49.25</v>
+        <v>36.565650000000012</v>
       </c>
       <c r="Q4" s="1">
-        <v>47.38</v>
+        <v>33.933025000000001</v>
       </c>
       <c r="R4" s="1">
-        <v>47.365000000000002</v>
+        <v>35.352899999999998</v>
       </c>
       <c r="S4" s="1">
-        <v>49.685000000000002</v>
+        <v>39.953375000000008</v>
       </c>
       <c r="T4" s="1">
-        <v>51.35</v>
+        <v>47.531224999999992</v>
       </c>
       <c r="U4" s="1">
-        <v>55.645000000000003</v>
+        <v>59.501250000000006</v>
       </c>
       <c r="V4" s="1">
-        <v>60.7</v>
+        <v>69.817262499999998</v>
       </c>
       <c r="W4" s="1">
-        <v>60</v>
+        <v>66.67295</v>
       </c>
       <c r="X4" s="1">
-        <v>53.854999999999997</v>
+        <v>60.631374999999998</v>
       </c>
       <c r="Y4" s="1">
-        <v>50.66</v>
+        <v>60.902999999999992</v>
       </c>
       <c r="Z4" s="1">
-        <v>46.34</v>
+        <v>60.987850000000002</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
@@ -1805,76 +1805,76 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>65.330999999999989</v>
       </c>
       <c r="D5" s="1">
-        <v>23.31</v>
+        <v>66.395437499999986</v>
       </c>
       <c r="E5" s="1">
-        <v>24.08</v>
+        <v>64.843950000000007</v>
       </c>
       <c r="F5" s="1">
-        <v>24.2</v>
+        <v>63.312375000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>25.25</v>
+        <v>64.598300000000009</v>
       </c>
       <c r="H5" s="1">
-        <v>27.995000000000001</v>
+        <v>62.763525000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>29.41</v>
+        <v>67.108387499999992</v>
       </c>
       <c r="J5" s="1">
-        <v>24.99</v>
+        <v>65.098950000000002</v>
       </c>
       <c r="K5" s="1">
-        <v>16.899999999999999</v>
+        <v>51.123674999999992</v>
       </c>
       <c r="L5" s="1">
-        <v>6.75</v>
+        <v>40.077600000000004</v>
       </c>
       <c r="M5" s="1">
-        <v>5.65</v>
+        <v>34.983750000000008</v>
       </c>
       <c r="N5" s="1">
-        <v>4.7249999999999996</v>
+        <v>37.009424999999993</v>
       </c>
       <c r="O5" s="1">
-        <v>2.25</v>
+        <v>34.175874999999998</v>
       </c>
       <c r="P5" s="1">
-        <v>1.5649999999999999</v>
+        <v>34.043624999999999</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.27</v>
+        <v>29.746250000000003</v>
       </c>
       <c r="R5" s="1">
-        <v>1.625</v>
+        <v>29.711674999999996</v>
       </c>
       <c r="S5" s="1">
-        <v>2.5</v>
+        <v>33.264400000000002</v>
       </c>
       <c r="T5" s="1">
-        <v>7.585</v>
+        <v>38.537500000000001</v>
       </c>
       <c r="U5" s="1">
-        <v>16.899999999999999</v>
+        <v>48.698099999999997</v>
       </c>
       <c r="V5" s="1">
-        <v>24.56</v>
+        <v>65.268524999999997</v>
       </c>
       <c r="W5" s="1">
-        <v>29.655000000000001</v>
+        <v>70.05461249999999</v>
       </c>
       <c r="X5" s="1">
-        <v>28.815000000000001</v>
+        <v>67.220650000000006</v>
       </c>
       <c r="Y5" s="1">
-        <v>24.5</v>
+        <v>63.110024999999986</v>
       </c>
       <c r="Z5" s="1">
-        <v>36.215000000000003</v>
+        <v>63.3909375</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
@@ -1885,76 +1885,76 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>35.25</v>
+        <v>65.330999999999989</v>
       </c>
       <c r="D6" s="1">
-        <v>34.564999999999998</v>
+        <v>60.072062499999987</v>
       </c>
       <c r="E6" s="1">
-        <v>34.5</v>
+        <v>62.936775000000004</v>
       </c>
       <c r="F6" s="1">
-        <v>34.005000000000003</v>
+        <v>61.503450000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>34.42</v>
+        <v>63.977162500000013</v>
       </c>
       <c r="H6" s="1">
-        <v>33.5</v>
+        <v>64.031475</v>
       </c>
       <c r="I6" s="1">
-        <v>33.96</v>
+        <v>65.7526625</v>
       </c>
       <c r="J6" s="1">
-        <v>36.435000000000002</v>
+        <v>61.907825000000003</v>
       </c>
       <c r="K6" s="1">
-        <v>20.85</v>
+        <v>50.617499999999993</v>
       </c>
       <c r="L6" s="1">
-        <v>15</v>
+        <v>39.660125000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>9.41</v>
+        <v>37.193250000000006</v>
       </c>
       <c r="N6" s="1">
-        <v>10.215</v>
+        <v>34.8324</v>
       </c>
       <c r="O6" s="1">
-        <v>7.35</v>
+        <v>35.191000000000003</v>
       </c>
       <c r="P6" s="1">
-        <v>4.83</v>
+        <v>30.801374999999997</v>
       </c>
       <c r="Q6" s="1">
-        <v>4.1050000000000004</v>
+        <v>30.936100000000007</v>
       </c>
       <c r="R6" s="1">
-        <v>3.72</v>
+        <v>30.594199999999997</v>
       </c>
       <c r="S6" s="1">
-        <v>7.35</v>
+        <v>32.304850000000002</v>
       </c>
       <c r="T6" s="1">
-        <v>9.7200000000000006</v>
+        <v>37.381375000000006</v>
       </c>
       <c r="U6" s="1">
-        <v>17.395</v>
+        <v>47.714299999999994</v>
       </c>
       <c r="V6" s="1">
-        <v>31.364999999999998</v>
+        <v>66.548299999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>34.005000000000003</v>
+        <v>75.110100000000003</v>
       </c>
       <c r="X6" s="1">
-        <v>33.384999999999998</v>
+        <v>65.848799999999997</v>
       </c>
       <c r="Y6" s="1">
-        <v>31.54</v>
+        <v>66.297399999999982</v>
       </c>
       <c r="Z6" s="1">
-        <v>36</v>
+        <v>63.3909375</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -1965,76 +1965,76 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>34.450000000000003</v>
+        <v>67.252499999999998</v>
       </c>
       <c r="D7" s="1">
-        <v>32.950000000000003</v>
+        <v>65.130762499999989</v>
       </c>
       <c r="E7" s="1">
-        <v>33.159999999999997</v>
+        <v>62.301050000000004</v>
       </c>
       <c r="F7" s="1">
-        <v>32.380000000000003</v>
+        <v>57.282624999999996</v>
       </c>
       <c r="G7" s="1">
-        <v>33.94</v>
+        <v>60.250337500000015</v>
       </c>
       <c r="H7" s="1">
-        <v>31.45</v>
+        <v>63.397500000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>33.215000000000003</v>
+        <v>71.175562499999998</v>
       </c>
       <c r="J7" s="1">
-        <v>29.29</v>
+        <v>64.460724999999996</v>
       </c>
       <c r="K7" s="1">
-        <v>19.324999999999999</v>
+        <v>49.098974999999989</v>
       </c>
       <c r="L7" s="1">
-        <v>12.085000000000001</v>
+        <v>42.582450000000001</v>
       </c>
       <c r="M7" s="1">
-        <v>11</v>
+        <v>38.298000000000002</v>
       </c>
       <c r="N7" s="1">
-        <v>10.88</v>
+        <v>35.9209125</v>
       </c>
       <c r="O7" s="1">
-        <v>5.86</v>
+        <v>33.499124999999999</v>
       </c>
       <c r="P7" s="1">
-        <v>5.1150000000000002</v>
+        <v>31.774049999999999</v>
       </c>
       <c r="Q7" s="1">
-        <v>1.625</v>
+        <v>28.258937500000002</v>
       </c>
       <c r="R7" s="1">
-        <v>1.625</v>
+        <v>30.005849999999995</v>
       </c>
       <c r="S7" s="1">
-        <v>4.2350000000000003</v>
+        <v>31.984999999999999</v>
       </c>
       <c r="T7" s="1">
-        <v>12.55</v>
+        <v>38.922875000000005</v>
       </c>
       <c r="U7" s="1">
-        <v>20.6</v>
+        <v>50.665699999999994</v>
       </c>
       <c r="V7" s="1">
-        <v>28.62</v>
+        <v>62.708975000000002</v>
       </c>
       <c r="W7" s="1">
-        <v>37.314999999999998</v>
+        <v>73.665675000000007</v>
       </c>
       <c r="X7" s="1">
-        <v>33.94</v>
+        <v>66.534724999999995</v>
       </c>
       <c r="Y7" s="1">
-        <v>35.5</v>
+        <v>66.934874999999977</v>
       </c>
       <c r="Z7" s="1">
-        <v>36</v>
+        <v>62.750624999999999</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
@@ -2045,76 +2045,76 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>56.57</v>
+        <v>73.44</v>
       </c>
       <c r="D8" s="1">
-        <v>56.19</v>
+        <v>70.869149999999991</v>
       </c>
       <c r="E8" s="1">
-        <v>56.32</v>
+        <v>68.526862500000007</v>
       </c>
       <c r="F8" s="1">
-        <v>56.29</v>
+        <v>67.360800000000012</v>
       </c>
       <c r="G8" s="1">
-        <v>56.44</v>
+        <v>67.09</v>
       </c>
       <c r="H8" s="1">
-        <v>58.42</v>
+        <v>72.779200000000003</v>
       </c>
       <c r="I8" s="1">
-        <v>60.36</v>
+        <v>73.089437500000003</v>
       </c>
       <c r="J8" s="1">
-        <v>58.42</v>
+        <v>79.457499999999996</v>
       </c>
       <c r="K8" s="1">
-        <v>56.41</v>
+        <v>78.807299999999998</v>
       </c>
       <c r="L8" s="1">
-        <v>55.96</v>
+        <v>71.036625000000015</v>
       </c>
       <c r="M8" s="1">
-        <v>49</v>
+        <v>64.039424999999994</v>
       </c>
       <c r="N8" s="1">
-        <v>46.49</v>
+        <v>58.098750000000003</v>
       </c>
       <c r="O8" s="1">
-        <v>46.395000000000003</v>
+        <v>56.995987500000012</v>
       </c>
       <c r="P8" s="1">
-        <v>44.494999999999997</v>
+        <v>54.863687499999997</v>
       </c>
       <c r="Q8" s="1">
-        <v>41.5</v>
+        <v>55.085749999999997</v>
       </c>
       <c r="R8" s="1">
-        <v>40.9</v>
+        <v>61.500037500000005</v>
       </c>
       <c r="S8" s="1">
-        <v>40.9</v>
+        <v>70.221537499999997</v>
       </c>
       <c r="T8" s="1">
-        <v>47.185000000000002</v>
+        <v>75.865475000000004</v>
       </c>
       <c r="U8" s="1">
-        <v>54.6</v>
+        <v>92.438062500000001</v>
       </c>
       <c r="V8" s="1">
-        <v>58.8</v>
+        <v>95.543400000000005</v>
       </c>
       <c r="W8" s="1">
-        <v>66.33</v>
+        <v>91.109750000000005</v>
       </c>
       <c r="X8" s="1">
-        <v>62.75</v>
+        <v>94.477687500000016</v>
       </c>
       <c r="Y8" s="1">
-        <v>58.57</v>
+        <v>82.683750000000003</v>
       </c>
       <c r="Z8" s="1">
-        <v>56.92</v>
+        <v>72.373199999999997</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
@@ -2125,76 +2125,76 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>53.61</v>
+        <v>74.174399999999991</v>
       </c>
       <c r="D9" s="1">
-        <v>53.604999999999997</v>
+        <v>73.016699999999986</v>
       </c>
       <c r="E9" s="1">
-        <v>53.604999999999997</v>
+        <v>67.820400000000006</v>
       </c>
       <c r="F9" s="1">
-        <v>47.5</v>
+        <v>66.040000000000006</v>
       </c>
       <c r="G9" s="1">
-        <v>51.22</v>
+        <v>68.43180000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>52.5</v>
+        <v>66.481000000000009</v>
       </c>
       <c r="I9" s="1">
-        <v>57.55</v>
+        <v>80.0137</v>
       </c>
       <c r="J9" s="1">
-        <v>51.22</v>
+        <v>76.279200000000003</v>
       </c>
       <c r="K9" s="1">
-        <v>43.984999999999999</v>
+        <v>74.260725000000008</v>
       </c>
       <c r="L9" s="1">
-        <v>39.695</v>
+        <v>71.733062500000017</v>
       </c>
       <c r="M9" s="1">
-        <v>39.799999999999997</v>
+        <v>60.272399999999998</v>
       </c>
       <c r="N9" s="1">
-        <v>40.549999999999997</v>
+        <v>56.355787500000005</v>
       </c>
       <c r="O9" s="1">
-        <v>41</v>
+        <v>59.933925000000009</v>
       </c>
       <c r="P9" s="1">
-        <v>41.244999999999997</v>
+        <v>60.638812499999993</v>
       </c>
       <c r="Q9" s="1">
-        <v>39.799999999999997</v>
+        <v>58.56485</v>
       </c>
       <c r="R9" s="1">
-        <v>39.799999999999997</v>
+        <v>59.636400000000002</v>
       </c>
       <c r="S9" s="1">
-        <v>41</v>
+        <v>67.494487499999991</v>
       </c>
       <c r="T9" s="1">
-        <v>42.115000000000002</v>
+        <v>76.639612499999998</v>
       </c>
       <c r="U9" s="1">
-        <v>44.5</v>
+        <v>88.036249999999995</v>
       </c>
       <c r="V9" s="1">
-        <v>58.1</v>
+        <v>95.543400000000005</v>
       </c>
       <c r="W9" s="1">
-        <v>64.45</v>
+        <v>99.741200000000006</v>
       </c>
       <c r="X9" s="1">
-        <v>61.21</v>
+        <v>85.479812500000008</v>
       </c>
       <c r="Y9" s="1">
-        <v>57.79</v>
+        <v>83.5105875</v>
       </c>
       <c r="Z9" s="1">
-        <v>53.875</v>
+        <v>76.142637500000006</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
@@ -2205,76 +2205,76 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>54.32</v>
+        <v>74.908799999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>52.314999999999998</v>
+        <v>74.448399999999992</v>
       </c>
       <c r="E10" s="1">
-        <v>52.625</v>
+        <v>70.646250000000009</v>
       </c>
       <c r="F10" s="1">
-        <v>46.814999999999998</v>
+        <v>64.058800000000005</v>
       </c>
       <c r="G10" s="1">
-        <v>47.185000000000002</v>
+        <v>67.760900000000007</v>
       </c>
       <c r="H10" s="1">
-        <v>49.725000000000001</v>
+        <v>67.180800000000005</v>
       </c>
       <c r="I10" s="1">
-        <v>56.65</v>
+        <v>75.397525000000002</v>
       </c>
       <c r="J10" s="1">
-        <v>54.935000000000002</v>
+        <v>78.662925000000001</v>
       </c>
       <c r="K10" s="1">
-        <v>45</v>
+        <v>79.56506250000001</v>
       </c>
       <c r="L10" s="1">
-        <v>37.5</v>
+        <v>71.036625000000015</v>
       </c>
       <c r="M10" s="1">
-        <v>32.44</v>
+        <v>65.922937500000003</v>
       </c>
       <c r="N10" s="1">
-        <v>32.274999999999999</v>
+        <v>60.422700000000006</v>
       </c>
       <c r="O10" s="1">
-        <v>32.494999999999997</v>
+        <v>58.758750000000006</v>
       </c>
       <c r="P10" s="1">
-        <v>32.44</v>
+        <v>56.018712499999999</v>
       </c>
       <c r="Q10" s="1">
-        <v>31.684999999999999</v>
+        <v>57.405150000000006</v>
       </c>
       <c r="R10" s="1">
-        <v>30</v>
+        <v>63.984887500000006</v>
       </c>
       <c r="S10" s="1">
-        <v>31.954999999999998</v>
+        <v>69.539775000000006</v>
       </c>
       <c r="T10" s="1">
-        <v>34.994999999999997</v>
+        <v>80.510300000000001</v>
       </c>
       <c r="U10" s="1">
-        <v>42.765000000000001</v>
+        <v>85.395162499999984</v>
       </c>
       <c r="V10" s="1">
-        <v>54.51</v>
+        <v>93.67</v>
       </c>
       <c r="W10" s="1">
-        <v>57.13</v>
+        <v>98.782150000000001</v>
       </c>
       <c r="X10" s="1">
-        <v>54.27</v>
+        <v>91.778325000000009</v>
       </c>
       <c r="Y10" s="1">
-        <v>47.09</v>
+        <v>78.549562500000008</v>
       </c>
       <c r="Z10" s="1">
-        <v>37.115000000000002</v>
+        <v>79.158187499999997</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
@@ -2285,76 +2285,76 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>46.02</v>
+        <v>64.454075000000003</v>
       </c>
       <c r="D11" s="1">
-        <v>44.98</v>
+        <v>67.09631250000001</v>
       </c>
       <c r="E11" s="1">
-        <v>45.034999999999997</v>
+        <v>63.62438749999999</v>
       </c>
       <c r="F11" s="1">
-        <v>41.91</v>
+        <v>56.514312500000003</v>
       </c>
       <c r="G11" s="1">
-        <v>42.68</v>
+        <v>58.159324999999995</v>
       </c>
       <c r="H11" s="1">
-        <v>44.945</v>
+        <v>60.141375000000011</v>
       </c>
       <c r="I11" s="1">
-        <v>52.07</v>
+        <v>64.3536</v>
       </c>
       <c r="J11" s="1">
-        <v>60.575000000000003</v>
+        <v>77.328125</v>
       </c>
       <c r="K11" s="1">
-        <v>60.375</v>
+        <v>83.567324999999997</v>
       </c>
       <c r="L11" s="1">
-        <v>59.02</v>
+        <v>81.541200000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>49.94</v>
+        <v>68.942999999999998</v>
       </c>
       <c r="N11" s="1">
-        <v>46.66</v>
+        <v>61.8241625</v>
       </c>
       <c r="O11" s="1">
-        <v>45.695</v>
+        <v>65.802099999999996</v>
       </c>
       <c r="P11" s="1">
-        <v>45.05</v>
+        <v>64.131662500000004</v>
       </c>
       <c r="Q11" s="1">
-        <v>46.2</v>
+        <v>60.060187500000005</v>
       </c>
       <c r="R11" s="1">
-        <v>54.82</v>
+        <v>67.045474999999996</v>
       </c>
       <c r="S11" s="1">
-        <v>60.47</v>
+        <v>77.729599999999991</v>
       </c>
       <c r="T11" s="1">
-        <v>67.62</v>
+        <v>90.87260000000002</v>
       </c>
       <c r="U11" s="1">
-        <v>80.27</v>
+        <v>93.43012499999999</v>
       </c>
       <c r="V11" s="1">
-        <v>75.760000000000005</v>
+        <v>100.38894999999998</v>
       </c>
       <c r="W11" s="1">
-        <v>61.5</v>
+        <v>87.797812500000006</v>
       </c>
       <c r="X11" s="1">
-        <v>59.14</v>
+        <v>87.765012500000012</v>
       </c>
       <c r="Y11" s="1">
-        <v>59.14</v>
+        <v>75.274437500000019</v>
       </c>
       <c r="Z11" s="1">
-        <v>54.82</v>
+        <v>74.325900000000004</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
@@ -2365,76 +2365,76 @@
         <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>40</v>
+        <v>65.118549999999999</v>
       </c>
       <c r="D12" s="1">
-        <v>38.395000000000003</v>
+        <v>67.09631250000001</v>
       </c>
       <c r="E12" s="1">
-        <v>37.5</v>
+        <v>63.62438749999999</v>
       </c>
       <c r="F12" s="1">
-        <v>36.295000000000002</v>
+        <v>61.273412500000013</v>
       </c>
       <c r="G12" s="1">
-        <v>35.494999999999997</v>
+        <v>58.159324999999995</v>
       </c>
       <c r="H12" s="1">
-        <v>38.5</v>
+        <v>58.914000000000009</v>
       </c>
       <c r="I12" s="1">
-        <v>44.195</v>
+        <v>66.364649999999997</v>
       </c>
       <c r="J12" s="1">
-        <v>53.68</v>
+        <v>74.265625</v>
       </c>
       <c r="K12" s="1">
-        <v>60.79</v>
+        <v>80.290174999999991</v>
       </c>
       <c r="L12" s="1">
-        <v>51.4</v>
+        <v>76.052849999999992</v>
       </c>
       <c r="M12" s="1">
-        <v>46.6</v>
+        <v>69.646500000000003</v>
       </c>
       <c r="N12" s="1">
-        <v>42.52</v>
+        <v>61.186800000000005</v>
       </c>
       <c r="O12" s="1">
-        <v>44.454999999999998</v>
+        <v>65.169387499999999</v>
       </c>
       <c r="P12" s="1">
-        <v>42.655000000000001</v>
+        <v>62.263750000000002</v>
       </c>
       <c r="Q12" s="1">
-        <v>42.755000000000003</v>
+        <v>61.956825000000002</v>
       </c>
       <c r="R12" s="1">
-        <v>47.75</v>
+        <v>64.993062499999994</v>
       </c>
       <c r="S12" s="1">
-        <v>56.5</v>
+        <v>76.959999999999994</v>
       </c>
       <c r="T12" s="1">
-        <v>65</v>
+        <v>83.882400000000018</v>
       </c>
       <c r="U12" s="1">
-        <v>67.069999999999993</v>
+        <v>101.29792499999999</v>
       </c>
       <c r="V12" s="1">
-        <v>67.504999999999995</v>
+        <v>102.33824999999999</v>
       </c>
       <c r="W12" s="1">
-        <v>74.36</v>
+        <v>95.191312500000009</v>
       </c>
       <c r="X12" s="1">
-        <v>67.17</v>
+        <v>82.652487500000007</v>
       </c>
       <c r="Y12" s="1">
-        <v>57.6</v>
+        <v>76.859162500000011</v>
       </c>
       <c r="Z12" s="1">
-        <v>51</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
@@ -2445,76 +2445,76 @@
         <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>43.24</v>
+        <v>68.440925000000007</v>
       </c>
       <c r="D13" s="1">
-        <v>40.854999999999997</v>
+        <v>65.818287500000011</v>
       </c>
       <c r="E13" s="1">
-        <v>37.5</v>
+        <v>62.388962499999998</v>
       </c>
       <c r="F13" s="1">
-        <v>35.35</v>
+        <v>61.273412500000013</v>
       </c>
       <c r="G13" s="1">
-        <v>35.340000000000003</v>
+        <v>59.939712499999999</v>
       </c>
       <c r="H13" s="1">
-        <v>35.83</v>
+        <v>58.914000000000009</v>
       </c>
       <c r="I13" s="1">
-        <v>36.92</v>
+        <v>68.375699999999995</v>
       </c>
       <c r="J13" s="1">
-        <v>39</v>
+        <v>80.390625</v>
       </c>
       <c r="K13" s="1">
-        <v>36.545000000000002</v>
+        <v>82.748037499999995</v>
       </c>
       <c r="L13" s="1">
-        <v>35</v>
+        <v>77.620950000000008</v>
       </c>
       <c r="M13" s="1">
-        <v>33.354999999999997</v>
+        <v>68.942999999999998</v>
       </c>
       <c r="N13" s="1">
-        <v>23.9</v>
+        <v>60.549437499999996</v>
       </c>
       <c r="O13" s="1">
-        <v>24.995000000000001</v>
+        <v>66.434812499999992</v>
       </c>
       <c r="P13" s="1">
-        <v>25.12</v>
+        <v>63.509025000000001</v>
       </c>
       <c r="Q13" s="1">
-        <v>30</v>
+        <v>60.060187500000005</v>
       </c>
       <c r="R13" s="1">
-        <v>35.215000000000003</v>
+        <v>70.466162499999996</v>
       </c>
       <c r="S13" s="1">
-        <v>41.88</v>
+        <v>73.881599999999992</v>
       </c>
       <c r="T13" s="1">
-        <v>52.74</v>
+        <v>88.251275000000007</v>
       </c>
       <c r="U13" s="1">
-        <v>62.94</v>
+        <v>100.31444999999999</v>
       </c>
       <c r="V13" s="1">
-        <v>60.005000000000003</v>
+        <v>100.38894999999998</v>
       </c>
       <c r="W13" s="1">
-        <v>59.85</v>
+        <v>88.722000000000008</v>
       </c>
       <c r="X13" s="1">
-        <v>55.375</v>
+        <v>83.504575000000003</v>
       </c>
       <c r="Y13" s="1">
-        <v>50.545000000000002</v>
+        <v>76.066800000000015</v>
       </c>
       <c r="Z13" s="1">
-        <v>47.825000000000003</v>
+        <v>72.854100000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/Market Data/CS7_market_data.xlsx
+++ b/data/CS7/Market Data/CS7_market_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3764F0C-D9D2-4183-9609-11D460B33DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D917E-B370-4C1E-97E4-9D9899348410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21375" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Growth Factors" sheetId="1" r:id="rId1"/>
@@ -515,76 +515,76 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>91.75</v>
+        <v>97.25500000000001</v>
       </c>
       <c r="D2" s="1">
-        <v>86.18</v>
+        <v>91.350800000000007</v>
       </c>
       <c r="E2" s="1">
-        <v>82.1</v>
+        <v>87.025999999999996</v>
       </c>
       <c r="F2" s="1">
-        <v>80</v>
+        <v>84.800000000000011</v>
       </c>
       <c r="G2" s="1">
-        <v>79.599999999999994</v>
+        <v>84.376000000000005</v>
       </c>
       <c r="H2" s="1">
-        <v>81.099999999999994</v>
+        <v>85.965999999999994</v>
       </c>
       <c r="I2" s="1">
-        <v>85.91</v>
+        <v>91.064599999999999</v>
       </c>
       <c r="J2" s="1">
-        <v>102.05</v>
+        <v>108.173</v>
       </c>
       <c r="K2" s="1">
-        <v>113.84</v>
+        <v>120.67040000000001</v>
       </c>
       <c r="L2" s="1">
-        <v>110</v>
+        <v>116.60000000000001</v>
       </c>
       <c r="M2" s="1">
-        <v>97.63</v>
+        <v>103.48780000000001</v>
       </c>
       <c r="N2" s="1">
-        <v>86.18</v>
+        <v>91.350800000000007</v>
       </c>
       <c r="O2" s="1">
-        <v>83.89</v>
+        <v>88.923400000000001</v>
       </c>
       <c r="P2" s="1">
-        <v>82.18</v>
+        <v>87.110800000000012</v>
       </c>
       <c r="Q2" s="1">
-        <v>83</v>
+        <v>87.98</v>
       </c>
       <c r="R2" s="1">
-        <v>85</v>
+        <v>90.100000000000009</v>
       </c>
       <c r="S2" s="1">
-        <v>97.63</v>
+        <v>103.48780000000001</v>
       </c>
       <c r="T2" s="1">
-        <v>118.5</v>
+        <v>125.61</v>
       </c>
       <c r="U2" s="1">
-        <v>128.93</v>
+        <v>136.66580000000002</v>
       </c>
       <c r="V2" s="1">
-        <v>132.31</v>
+        <v>140.24860000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>117.93</v>
+        <v>125.00580000000001</v>
       </c>
       <c r="X2" s="1">
-        <v>108.33</v>
+        <v>114.82980000000001</v>
       </c>
       <c r="Y2" s="1">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Z2" s="1">
-        <v>93.26</v>
+        <v>98.85560000000001</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -595,76 +595,76 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>88.98</v>
+        <v>97.878000000000014</v>
       </c>
       <c r="D3" s="1">
-        <v>86.45</v>
+        <v>95.095000000000013</v>
       </c>
       <c r="E3" s="1">
-        <v>84.99</v>
+        <v>93.489000000000004</v>
       </c>
       <c r="F3" s="1">
-        <v>83</v>
+        <v>91.300000000000011</v>
       </c>
       <c r="G3" s="1">
-        <v>83.14</v>
+        <v>91.454000000000008</v>
       </c>
       <c r="H3" s="1">
-        <v>85</v>
+        <v>93.500000000000014</v>
       </c>
       <c r="I3" s="1">
-        <v>89</v>
+        <v>97.9</v>
       </c>
       <c r="J3" s="1">
-        <v>100</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="K3" s="1">
-        <v>104.77</v>
+        <v>115.247</v>
       </c>
       <c r="L3" s="1">
-        <v>105</v>
+        <v>115.50000000000001</v>
       </c>
       <c r="M3" s="1">
-        <v>100</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="N3" s="1">
-        <v>94.58</v>
+        <v>104.03800000000001</v>
       </c>
       <c r="O3" s="1">
-        <v>92</v>
+        <v>101.2</v>
       </c>
       <c r="P3" s="1">
-        <v>91.78</v>
+        <v>100.95800000000001</v>
       </c>
       <c r="Q3" s="1">
-        <v>90.1</v>
+        <v>99.11</v>
       </c>
       <c r="R3" s="1">
-        <v>92.01</v>
+        <v>101.21100000000001</v>
       </c>
       <c r="S3" s="1">
-        <v>100.98</v>
+        <v>111.07800000000002</v>
       </c>
       <c r="T3" s="1">
-        <v>107.1</v>
+        <v>117.81</v>
       </c>
       <c r="U3" s="1">
-        <v>126</v>
+        <v>138.60000000000002</v>
       </c>
       <c r="V3" s="1">
-        <v>119.47</v>
+        <v>131.417</v>
       </c>
       <c r="W3" s="1">
-        <v>110</v>
+        <v>121.00000000000001</v>
       </c>
       <c r="X3" s="1">
-        <v>102.26</v>
+        <v>112.48600000000002</v>
       </c>
       <c r="Y3" s="1">
-        <v>98</v>
+        <v>107.80000000000001</v>
       </c>
       <c r="Z3" s="1">
-        <v>95.49</v>
+        <v>105.039</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
@@ -675,76 +675,76 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>92.33</v>
+        <v>100.6397</v>
       </c>
       <c r="D4" s="1">
-        <v>90.12</v>
+        <v>98.230800000000016</v>
       </c>
       <c r="E4" s="1">
-        <v>87.01</v>
+        <v>94.840900000000019</v>
       </c>
       <c r="F4" s="1">
-        <v>85.8</v>
+        <v>93.522000000000006</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>92.65</v>
       </c>
       <c r="H4" s="1">
-        <v>86.3</v>
+        <v>94.067000000000007</v>
       </c>
       <c r="I4" s="1">
-        <v>95</v>
+        <v>103.55000000000001</v>
       </c>
       <c r="J4" s="1">
-        <v>103.94</v>
+        <v>113.2946</v>
       </c>
       <c r="K4" s="1">
-        <v>121.4</v>
+        <v>132.32600000000002</v>
       </c>
       <c r="L4" s="1">
-        <v>121.4</v>
+        <v>132.32600000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>105.38</v>
+        <v>114.8642</v>
       </c>
       <c r="N4" s="1">
-        <v>102.97</v>
+        <v>112.2373</v>
       </c>
       <c r="O4" s="1">
-        <v>99.99</v>
+        <v>108.98910000000001</v>
       </c>
       <c r="P4" s="1">
-        <v>98.5</v>
+        <v>107.36500000000001</v>
       </c>
       <c r="Q4" s="1">
-        <v>94.76</v>
+        <v>103.28840000000001</v>
       </c>
       <c r="R4" s="1">
-        <v>94.73</v>
+        <v>103.25570000000002</v>
       </c>
       <c r="S4" s="1">
-        <v>99.37</v>
+        <v>108.31330000000001</v>
       </c>
       <c r="T4" s="1">
-        <v>102.7</v>
+        <v>111.94300000000001</v>
       </c>
       <c r="U4" s="1">
-        <v>111.29</v>
+        <v>121.30610000000001</v>
       </c>
       <c r="V4" s="1">
-        <v>121.4</v>
+        <v>132.32600000000002</v>
       </c>
       <c r="W4" s="1">
-        <v>120</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="X4" s="1">
-        <v>107.71</v>
+        <v>117.40390000000001</v>
       </c>
       <c r="Y4" s="1">
-        <v>101.32</v>
+        <v>110.4388</v>
       </c>
       <c r="Z4" s="1">
-        <v>92.68</v>
+        <v>101.02120000000002</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
@@ -1565,76 +1565,76 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>57.62807500000001</v>
+        <v>61.085759500000016</v>
       </c>
       <c r="D2" s="1">
-        <v>55.55</v>
+        <v>58.883000000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>53.603549999999998</v>
+        <v>56.819763000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>56.433562500000001</v>
+        <v>59.819576250000004</v>
       </c>
       <c r="G2" s="1">
-        <v>53.282600000000002</v>
+        <v>56.479556000000002</v>
       </c>
       <c r="H2" s="1">
-        <v>54.786250000000003</v>
+        <v>58.073425000000007</v>
       </c>
       <c r="I2" s="1">
-        <v>60.200399999999988</v>
+        <v>63.812423999999993</v>
       </c>
       <c r="J2" s="1">
-        <v>61.536774999999999</v>
+        <v>65.228981500000003</v>
       </c>
       <c r="K2" s="1">
-        <v>56.202299999999994</v>
+        <v>59.574437999999994</v>
       </c>
       <c r="L2" s="1">
-        <v>51.013837500000001</v>
+        <v>54.074667750000003</v>
       </c>
       <c r="M2" s="1">
-        <v>43.947337500000003</v>
+        <v>46.584177750000009</v>
       </c>
       <c r="N2" s="1">
-        <v>42.340462500000001</v>
+        <v>44.88089025</v>
       </c>
       <c r="O2" s="1">
-        <v>36.816000000000003</v>
+        <v>39.024960000000007</v>
       </c>
       <c r="P2" s="1">
-        <v>36.565650000000012</v>
+        <v>38.759589000000013</v>
       </c>
       <c r="Q2" s="1">
-        <v>34.282850000000003</v>
+        <v>36.339821000000008</v>
       </c>
       <c r="R2" s="1">
-        <v>34.995800000000003</v>
+        <v>37.095548000000008</v>
       </c>
       <c r="S2" s="1">
-        <v>41.176437499999999</v>
+        <v>43.647023750000002</v>
       </c>
       <c r="T2" s="1">
-        <v>48.501249999999999</v>
+        <v>51.411324999999998</v>
       </c>
       <c r="U2" s="1">
-        <v>59.501250000000006</v>
+        <v>63.071325000000009</v>
       </c>
       <c r="V2" s="1">
-        <v>65.750237499999997</v>
+        <v>69.695251749999997</v>
       </c>
       <c r="W2" s="1">
-        <v>72.171750000000003</v>
+        <v>76.502055000000013</v>
       </c>
       <c r="X2" s="1">
-        <v>60.631374999999998</v>
+        <v>64.269257499999995</v>
       </c>
       <c r="Y2" s="1">
-        <v>62.711999999999996</v>
+        <v>66.474720000000005</v>
       </c>
       <c r="Z2" s="1">
-        <v>61.610174999999998</v>
+        <v>65.306785500000004</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -1645,76 +1645,76 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>55.345775000000003</v>
+        <v>54.792317250000004</v>
       </c>
       <c r="D3" s="1">
-        <v>58.327500000000001</v>
+        <v>57.744225</v>
       </c>
       <c r="E3" s="1">
-        <v>57.432374999999993</v>
+        <v>56.858051249999995</v>
       </c>
       <c r="F3" s="1">
-        <v>53.2087875</v>
+        <v>52.676699624999998</v>
       </c>
       <c r="G3" s="1">
-        <v>53.826300000000003</v>
+        <v>53.288037000000003</v>
       </c>
       <c r="H3" s="1">
-        <v>57.525562499999999</v>
+        <v>56.950306874999995</v>
       </c>
       <c r="I3" s="1">
-        <v>60.200399999999988</v>
+        <v>59.598395999999987</v>
       </c>
       <c r="J3" s="1">
-        <v>62.755324999999992</v>
+        <v>62.127771749999994</v>
       </c>
       <c r="K3" s="1">
-        <v>59.040799999999997</v>
+        <v>58.450391999999994</v>
       </c>
       <c r="L3" s="1">
-        <v>49.498575000000002</v>
+        <v>49.003589250000005</v>
       </c>
       <c r="M3" s="1">
-        <v>45.279075000000006</v>
+        <v>44.826284250000008</v>
       </c>
       <c r="N3" s="1">
-        <v>41.5020375</v>
+        <v>41.087017125000003</v>
       </c>
       <c r="O3" s="1">
-        <v>37.1995</v>
+        <v>36.827505000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>36.196300000000008</v>
+        <v>35.834337000000005</v>
       </c>
       <c r="Q3" s="1">
-        <v>33.583200000000005</v>
+        <v>33.247368000000002</v>
       </c>
       <c r="R3" s="1">
-        <v>36.781300000000002</v>
+        <v>36.413487000000003</v>
       </c>
       <c r="S3" s="1">
-        <v>39.953375000000008</v>
+        <v>39.553841250000005</v>
       </c>
       <c r="T3" s="1">
-        <v>46.076187499999996</v>
+        <v>45.615425624999993</v>
       </c>
       <c r="U3" s="1">
-        <v>57.716212500000005</v>
+        <v>57.139050375000004</v>
       </c>
       <c r="V3" s="1">
-        <v>69.817262499999998</v>
+        <v>69.119089875</v>
       </c>
       <c r="W3" s="1">
-        <v>68.047650000000004</v>
+        <v>67.367173500000007</v>
       </c>
       <c r="X3" s="1">
-        <v>62.546049999999994</v>
+        <v>61.920589499999991</v>
       </c>
       <c r="Y3" s="1">
-        <v>59.696999999999996</v>
+        <v>59.100029999999997</v>
       </c>
       <c r="Z3" s="1">
-        <v>60.365524999999998</v>
+        <v>59.761869749999995</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
@@ -1725,76 +1725,76 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>58.769225000000006</v>
+        <v>62.883070750000009</v>
       </c>
       <c r="D4" s="1">
-        <v>53.327999999999996</v>
+        <v>57.060960000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>56.338424999999987</v>
+        <v>60.282114749999991</v>
       </c>
       <c r="F4" s="1">
-        <v>54.283712499999993</v>
+        <v>58.083572374999996</v>
       </c>
       <c r="G4" s="1">
-        <v>57.088500000000003</v>
+        <v>61.084695000000011</v>
       </c>
       <c r="H4" s="1">
-        <v>55.334112499999989</v>
+        <v>59.207500374999995</v>
       </c>
       <c r="I4" s="1">
-        <v>56.727299999999993</v>
+        <v>60.698210999999993</v>
       </c>
       <c r="J4" s="1">
-        <v>60.318224999999991</v>
+        <v>64.540500749999993</v>
       </c>
       <c r="K4" s="1">
-        <v>56.77</v>
+        <v>60.743900000000004</v>
       </c>
       <c r="L4" s="1">
-        <v>53.034187500000002</v>
+        <v>56.746580625000007</v>
       </c>
       <c r="M4" s="1">
-        <v>45.279075000000006</v>
+        <v>48.448610250000009</v>
       </c>
       <c r="N4" s="1">
-        <v>39.825187499999998</v>
+        <v>42.612950625000003</v>
       </c>
       <c r="O4" s="1">
-        <v>37.1995</v>
+        <v>39.803465000000003</v>
       </c>
       <c r="P4" s="1">
-        <v>36.565650000000012</v>
+        <v>39.125245500000013</v>
       </c>
       <c r="Q4" s="1">
-        <v>33.933025000000001</v>
+        <v>36.308336750000002</v>
       </c>
       <c r="R4" s="1">
-        <v>35.352899999999998</v>
+        <v>37.827603000000003</v>
       </c>
       <c r="S4" s="1">
-        <v>39.953375000000008</v>
+        <v>42.75011125000001</v>
       </c>
       <c r="T4" s="1">
-        <v>47.531224999999992</v>
+        <v>50.858410749999997</v>
       </c>
       <c r="U4" s="1">
-        <v>59.501250000000006</v>
+        <v>63.666337500000012</v>
       </c>
       <c r="V4" s="1">
-        <v>69.817262499999998</v>
+        <v>74.704470874999998</v>
       </c>
       <c r="W4" s="1">
-        <v>66.67295</v>
+        <v>71.340056500000003</v>
       </c>
       <c r="X4" s="1">
-        <v>60.631374999999998</v>
+        <v>64.875571250000007</v>
       </c>
       <c r="Y4" s="1">
-        <v>60.902999999999992</v>
+        <v>65.166209999999992</v>
       </c>
       <c r="Z4" s="1">
-        <v>60.987850000000002</v>
+        <v>65.256999500000006</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
